--- a/output/laminas_comunales/comunal_s_isapre_a_2024_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_o_higgins.xlsx
@@ -375,106 +375,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C2">
-        <v>36512</v>
+        <v>32.09330985915493</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="C3">
-        <v>18229</v>
+        <v>13.94535218583618</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="C4">
-        <v>7389</v>
+        <v>11.93426372766401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C5">
-        <v>3872</v>
+        <v>10.83945310167771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C6">
-        <v>3631</v>
+        <v>8.865239717809665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="C7">
-        <v>3537</v>
+        <v>7.790270766406609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>2994</v>
+        <v>7.63492948085909</v>
       </c>
     </row>
     <row r="9">
@@ -489,217 +489,217 @@
         </is>
       </c>
       <c r="C9">
-        <v>2865</v>
+        <v>7.592018443437476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C10">
-        <v>1867</v>
+        <v>7.179129110067285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="C11">
-        <v>1830</v>
+        <v>7.037953795379538</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="C12">
-        <v>1781</v>
+        <v>6.944417175505075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C13">
-        <v>1706</v>
+        <v>6.798673872564604</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="C14">
-        <v>1482</v>
+        <v>6.719367588932807</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="C15">
-        <v>1356</v>
+        <v>6.407440455762235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="C16">
-        <v>1217</v>
+        <v>5.669106881405564</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Marchigüe</t>
         </is>
       </c>
       <c r="C17">
-        <v>1131</v>
+        <v>5.400818608365778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="C18">
-        <v>1075</v>
+        <v>5.28176336036598</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="C19">
-        <v>699</v>
+        <v>5.262642580897832</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="C20">
-        <v>689</v>
+        <v>5.188284518828452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="C21">
-        <v>679</v>
+        <v>5.094181665969025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="C22">
-        <v>663</v>
+        <v>4.934409687184662</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="C23">
-        <v>629</v>
+        <v>4.734361610968294</v>
       </c>
     </row>
     <row r="24">
@@ -714,112 +714,112 @@
         </is>
       </c>
       <c r="C24">
-        <v>621</v>
+        <v>4.536820572764465</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="C25">
-        <v>578</v>
+        <v>4.418082718820135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="C26">
-        <v>570</v>
+        <v>4.389059718401036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="C27">
-        <v>558</v>
+        <v>4.235880398671096</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marchigüe</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="C28">
-        <v>541</v>
+        <v>4.131634261692065</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="C29">
-        <v>489</v>
+        <v>3.742613263296126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="C30">
-        <v>430</v>
+        <v>3.480916030534351</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="C31">
-        <v>254</v>
+        <v>3.42684093082563</v>
       </c>
     </row>
     <row r="32">
@@ -834,22 +834,22 @@
         </is>
       </c>
       <c r="C32">
-        <v>240</v>
+        <v>3.244997295835587</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="C33">
-        <v>221</v>
+        <v>3.172801960873315</v>
       </c>
     </row>
     <row r="34">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>213</v>
+        <v>2.847974328118732</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
